--- a/Ocorrências GBIF.xlsx
+++ b/Ocorrências GBIF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faculdade\Laboratorio\lagostas_carapaca\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F49D91-45E4-49B9-B516-A0F081035BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3067FBCB-A5CD-4EE2-A371-0DD1FB9C76C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20880" yWindow="975" windowWidth="17520" windowHeight="13140" activeTab="2" xr2:uid="{86DDF78E-60EF-41D8-B405-4354A955066C}"/>
   </bookViews>
